--- a/templates/master-excel.xlsx
+++ b/templates/master-excel.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="topical_map" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="cluster_keywords" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="cannibalization" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="quick_wins" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="new_content_plan" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="content_improve" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="gsc_performance" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="content_decay" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="on_page_audit" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="opportunity" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="tech_seo" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="crawl_sitemap" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="robots_txt" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="schema" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="redirect_404" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="completed_work" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="master_task" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="topical_map" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cluster_keywords" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cannibalization" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quick_wins" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="new_content_plan" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="content_improve" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gsc_performance" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="content_decay" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="on_page_audit" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="opportunity" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tech_seo" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crawl_sitemap" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="robots_txt" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="schema" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="redirect_404" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="completed_work" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="master_task" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1176,7 +1176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:K3"/>
+  <dimension ref="A3:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="3">
@@ -1235,6 +1235,21 @@
           <t>lifecycle_status</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>image_prompt</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>alt_text</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/templates/master-excel.xlsx
+++ b/templates/master-excel.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:H4"/>
+  <dimension ref="A4:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -543,6 +543,16 @@
           <t>assigned_url_action</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>aio_presence</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>expected_uplift_clicks</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1110,7 +1120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:J4"/>
+  <dimension ref="A4:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -1164,6 +1174,26 @@
           <t>priority</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>aio_presence</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>aio_own_cited</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>aio_checked_date</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>expected_uplift_clicks</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/templates/master-excel.xlsx
+++ b/templates/master-excel.xlsx
@@ -25,6 +25,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="redirect_404" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="completed_work" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="master_task" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gbp_audit" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -926,6 +927,57 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A3:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>audit_id</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>audit_date</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>gap_description</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>recommended_action</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/templates/master-excel.xlsx
+++ b/templates/master-excel.xlsx
@@ -26,6 +26,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="completed_work" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="master_task" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gbp_audit" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfs_ranked_keywords" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="backlinks" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfs_relevant_pages" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1044,18 +1047,186 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A3:K3"/>
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A3:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>keyword</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rank_group</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>rank_absolute</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>search_volume</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>etv</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>cpc</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A3:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>referring_domains</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>referring_main_domains</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>referring_domains_nofollow</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>spam_score</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>last_updated</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A3:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ranked_keywords_count</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>etv</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pos_2_3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>pos_4_10</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>pos_11_20</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A3:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>cluster</t>
         </is>
       </c>
